--- a/data/interim/new-bills-parsed/Profile0412_pivoted.xlsx
+++ b/data/interim/new-bills-parsed/Profile0412_pivoted.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dimpl\OneDrive\Documents\GitHub\TroyBanks_Audit_Demo_VA\data\interim\new-bills-parsed\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB0A98A-CD29-4C21-A49F-AE1F9786B01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1516,8 +1522,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1580,13 +1586,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1624,7 +1638,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1658,6 +1672,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1692,9 +1707,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1867,11 +1883,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BA34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:53">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2032,7 +2048,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:53">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -2163,7 +2179,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:53">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -2294,7 +2310,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="1:53">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -2422,7 +2438,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="5" spans="1:53">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -2553,7 +2569,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="6" spans="1:53">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -2684,7 +2700,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:53">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -2815,7 +2831,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:53">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2946,7 +2962,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:53">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -3077,7 +3093,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="10" spans="1:53">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -3208,7 +3224,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="1:53">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -3345,7 +3361,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:53">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -3482,7 +3498,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="13" spans="1:53">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -3619,7 +3635,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="14" spans="1:53">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -3759,7 +3775,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:53">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -3896,7 +3912,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="16" spans="1:53">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -4036,7 +4052,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="17" spans="1:53">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -4173,7 +4189,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="18" spans="1:53">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -4313,7 +4329,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="1:53">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -4450,7 +4466,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:53">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -4578,7 +4594,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="21" spans="1:53">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -4718,7 +4734,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="22" spans="1:53">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -4861,7 +4877,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:53">
+    <row r="23" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -5001,7 +5017,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="24" spans="1:53">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -5138,7 +5154,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:53">
+    <row r="25" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -5278,7 +5294,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="26" spans="1:53">
+    <row r="26" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -5415,7 +5431,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="27" spans="1:53">
+    <row r="27" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -5555,7 +5571,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="28" spans="1:53">
+    <row r="28" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -5695,7 +5711,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:53">
+    <row r="29" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -5841,7 +5857,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="30" spans="1:53">
+    <row r="30" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -5987,7 +6003,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="31" spans="1:53">
+    <row r="31" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>55</v>
       </c>
@@ -6133,7 +6149,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="32" spans="1:53">
+    <row r="32" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>55</v>
       </c>
@@ -6279,7 +6295,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="1:53">
+    <row r="33" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -6428,7 +6444,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="34" spans="1:53">
+    <row r="34" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>55</v>
       </c>
